--- a/GATEWAY/A1#111#SOSEPEXX/SOSEPE_SRL/CAMILLA/FSE-2.0/accreditamento-checklist_V9.0.0.xlsx
+++ b/GATEWAY/A1#111#SOSEPEXX/SOSEPE_SRL/CAMILLA/FSE-2.0/accreditamento-checklist_V9.0.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.girotto\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.girotto\Downloads\fse2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4871A826-6C75-4680-A6A3-A55A5C76181E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F87F77-4CCB-4767-BBCF-7559E8CAB0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -2471,13 +2471,13 @@
     <t>Accreditamento già eseguito</t>
   </si>
   <si>
-    <t>2026-03-23T12:03:48Z</t>
-  </si>
-  <si>
-    <t>d919fae4f2eb203ab34e457ed99681df</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.30.4.4.27a082a5faf381858b6d36c87f953b2cbb50f3228419c852a3cd36dca334b7f2.90ee335427^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-27T11:57:33Z</t>
+  </si>
+  <si>
+    <t>c38d618c6191ac8aec696099165df76e</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.30.4.4.878654deb1e122f95b0bf9a9954e0cfa4fd206f34dc22ebde587d9b9e092e5c9.f78bb16b6c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -11874,7 +11874,7 @@
         <v>399</v>
       </c>
       <c r="F193" s="31">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="G193" s="31" t="s">
         <v>653</v>
